--- a/outputs/1 N NO 5_ch00_measurements.xlsx
+++ b/outputs/1 N NO 5_ch00_measurements.xlsx
@@ -241,7 +241,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="23260050" cy="8020050"/>
+    <ext cx="23231475" cy="8010525"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -301,7 +301,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7143750" cy="8420100"/>
+    <ext cx="7143750" cy="8401050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
